--- a/AffinityLossRunTemplate.xlsx
+++ b/AffinityLossRunTemplate.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record Only" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Claim Details'!$A$1:$BU$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Record Only'!$A$1:$AN$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Claim Details'!$A$1:$BQ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Record Only'!$A$1:$AK$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -207,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -287,6 +287,40 @@
     </xf>
     <xf numFmtId="168" fontId="1" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -364,6 +398,36 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>SAC Platform</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Calendar days from Loss Date to Date of Notice (Report Date). Blank when either date is missing. This is not the report generation date.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>SAC Platform</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Calendar days from Loss Date to Date of Notice (Report Date). Blank when either date is missing. This is not the report generation date.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -387,6 +451,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1005,629 +1072,422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU2"/>
+  <dimension ref="A1:BQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.7109375" customWidth="1" min="1" max="1"/>
     <col width="31.7109375" customWidth="1" min="2" max="2"/>
-    <col width="31.140625" customWidth="1" min="3" max="3"/>
-    <col width="13.5703125" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="15.28515625" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="11.28515625" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="28" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="31.140625" customWidth="1" min="12" max="12"/>
-    <col width="31.140625" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="26.42578125" customWidth="1" min="15" max="15"/>
-    <col width="13.42578125" customWidth="1" min="16" max="16"/>
-    <col width="15.85546875" customWidth="1" min="17" max="17"/>
-    <col hidden="1" width="21.42578125" customWidth="1" min="18" max="18"/>
-    <col width="9.85546875" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="21.5703125" customWidth="1" min="23" max="23"/>
-    <col width="27.7109375" customWidth="1" min="24" max="24"/>
-    <col width="14.28515625" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="17.28515625" customWidth="1" min="26" max="26"/>
-    <col width="13.85546875" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="18" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="16" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="14.7109375" customWidth="1" min="30" max="30"/>
-    <col hidden="1" width="20.42578125" customWidth="1" min="31" max="31"/>
-    <col hidden="1" width="11.28515625" customWidth="1" min="32" max="32"/>
-    <col hidden="1" width="19.140625" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="15.85546875" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="12.5703125" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="22.42578125" customWidth="1" min="36" max="36"/>
-    <col hidden="1" width="18.85546875" customWidth="1" min="37" max="37"/>
-    <col hidden="1" width="18.85546875" customWidth="1" min="38" max="38"/>
-    <col width="17" customWidth="1" min="39" max="39"/>
-    <col width="18.85546875" customWidth="1" min="40" max="40"/>
-    <col width="19.140625" customWidth="1" min="41" max="41"/>
-    <col hidden="1" width="9.42578125" customWidth="1" min="42" max="42"/>
-    <col hidden="1" width="15.85546875" customWidth="1" min="43" max="43"/>
-    <col hidden="1" width="21.42578125" customWidth="1" min="44" max="44"/>
-    <col hidden="1" width="20.5703125" customWidth="1" min="45" max="45"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="46" max="46"/>
-    <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="12.42578125" customWidth="1" min="48" max="48"/>
-    <col hidden="1" width="28" customWidth="1" min="49" max="49"/>
-    <col width="28" customWidth="1" min="50" max="50"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="31.140625" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="31.140625" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="21.5703125" customWidth="1" min="20" max="20"/>
+    <col width="27.7109375" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="17.28515625" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="20.42578125" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="19.140625" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="22.42578125" customWidth="1" min="33" max="33"/>
+    <col width="18.85546875" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="18.85546875" customWidth="1" min="36" max="36"/>
+    <col width="19.140625" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="31.140625" customWidth="1" min="40" max="40"/>
+    <col width="26.42578125" customWidth="1" min="41" max="41"/>
+    <col width="21.42578125" customWidth="1" min="42" max="42"/>
+    <col width="18.85546875" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="21.42578125" customWidth="1" min="46" max="46"/>
+    <col width="20.5703125" customWidth="1" min="47" max="47"/>
+    <col width="17" customWidth="1" min="48" max="48"/>
+    <col width="16.5703125" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
     <col width="26" customWidth="1" min="51" max="51"/>
-    <col hidden="1" width="17" customWidth="1" min="52" max="52"/>
-    <col hidden="1" width="16.5703125" customWidth="1" min="53" max="53"/>
-    <col hidden="1" width="16" customWidth="1" min="54" max="54"/>
-    <col hidden="1" width="26" customWidth="1" min="55" max="55"/>
-    <col hidden="1" width="12.85546875" customWidth="1" min="56" max="56"/>
-    <col hidden="1" width="22" customWidth="1" min="57" max="57"/>
-    <col hidden="1" width="14.5703125" customWidth="1" min="58" max="58"/>
-    <col hidden="1" width="19.5703125" customWidth="1" min="59" max="59"/>
-    <col hidden="1" width="12.5703125" customWidth="1" min="60" max="60"/>
-    <col hidden="1" width="21.140625" customWidth="1" min="61" max="61"/>
-    <col hidden="1" width="13.7109375" customWidth="1" min="62" max="62"/>
-    <col hidden="1" width="18.85546875" customWidth="1" min="63" max="63"/>
-    <col hidden="1" width="20.5703125" customWidth="1" min="64" max="64"/>
-    <col hidden="1" width="21" customWidth="1" min="65" max="65"/>
-    <col hidden="1" width="15.7109375" customWidth="1" min="66" max="66"/>
-    <col hidden="1" width="25.5703125" customWidth="1" min="67" max="67"/>
-    <col hidden="1" width="23.42578125" customWidth="1" min="68" max="68"/>
-    <col hidden="1" width="20" customWidth="1" min="69" max="69"/>
-    <col hidden="1" width="21.5703125" customWidth="1" min="70" max="70"/>
-    <col hidden="1" width="18.7109375" customWidth="1" min="71" max="71"/>
-    <col hidden="1" width="19.7109375" customWidth="1" min="72" max="72"/>
-    <col hidden="1" width="28" customWidth="1" min="73" max="73"/>
-    <col width="32.28515625" customWidth="1" min="74" max="74"/>
-    <col width="32.28515625" customWidth="1" min="75" max="75"/>
-    <col width="32.28515625" customWidth="1" min="76" max="76"/>
-    <col width="32.28515625" customWidth="1" min="77" max="77"/>
-    <col width="32.28515625" customWidth="1" min="78" max="78"/>
-    <col width="32.28515625" customWidth="1" min="79" max="79"/>
-    <col width="32.28515625" customWidth="1" min="80" max="80"/>
-    <col width="32.28515625" customWidth="1" min="81" max="81"/>
-    <col width="32.28515625" customWidth="1" min="82" max="82"/>
-    <col width="32.28515625" customWidth="1" min="83" max="83"/>
-    <col width="32.28515625" customWidth="1" min="84" max="84"/>
-    <col width="32.28515625" customWidth="1" min="85" max="85"/>
-    <col width="32.28515625" customWidth="1" min="86" max="86"/>
-    <col width="32.28515625" customWidth="1" min="87" max="87"/>
-    <col width="32.28515625" customWidth="1" min="88" max="88"/>
-    <col width="32.28515625" customWidth="1" min="89" max="89"/>
-    <col width="32.28515625" customWidth="1" min="90" max="90"/>
-    <col width="32.28515625" customWidth="1" min="91" max="91"/>
-    <col width="32.28515625" customWidth="1" min="92" max="92"/>
-    <col width="32.28515625" customWidth="1" min="93" max="93"/>
-    <col width="32.28515625" customWidth="1" min="94" max="94"/>
-    <col width="32.28515625" customWidth="1" min="95" max="95"/>
-    <col width="32.28515625" customWidth="1" min="96" max="96"/>
-    <col width="32.28515625" customWidth="1" min="97" max="97"/>
-    <col width="32.28515625" customWidth="1" min="98" max="98"/>
-    <col width="32.28515625" customWidth="1" min="99" max="99"/>
-    <col width="32.28515625" customWidth="1" min="100" max="100"/>
-    <col width="32.28515625" customWidth="1" min="101" max="101"/>
-    <col width="32.28515625" customWidth="1" min="102" max="102"/>
-    <col width="32.28515625" customWidth="1" min="103" max="103"/>
-    <col width="32.28515625" customWidth="1" min="104" max="104"/>
-    <col width="32.28515625" customWidth="1" min="105" max="105"/>
-    <col width="32.28515625" customWidth="1" min="106" max="106"/>
-    <col width="32.28515625" customWidth="1" min="107" max="107"/>
-    <col width="32.28515625" customWidth="1" min="108" max="108"/>
-    <col width="32.28515625" customWidth="1" min="109" max="109"/>
-    <col width="32.28515625" customWidth="1" min="110" max="110"/>
-    <col width="32.28515625" customWidth="1" min="111" max="111"/>
-    <col width="32.28515625" customWidth="1" min="112" max="112"/>
-    <col width="32.28515625" customWidth="1" min="113" max="113"/>
-    <col width="32.28515625" customWidth="1" min="114" max="114"/>
-    <col width="32.28515625" customWidth="1" min="115" max="115"/>
-    <col width="32.28515625" customWidth="1" min="116" max="116"/>
-    <col width="32.28515625" customWidth="1" min="117" max="117"/>
-    <col width="32.28515625" customWidth="1" min="118" max="118"/>
-    <col width="32.28515625" customWidth="1" min="119" max="119"/>
-    <col width="32.28515625" customWidth="1" min="120" max="120"/>
-    <col width="32.28515625" customWidth="1" min="121" max="121"/>
-    <col width="32.28515625" customWidth="1" min="122" max="122"/>
-    <col width="32.28515625" customWidth="1" min="123" max="123"/>
-    <col width="32.28515625" customWidth="1" min="124" max="124"/>
-    <col width="32.28515625" customWidth="1" min="125" max="125"/>
-    <col width="32.28515625" customWidth="1" min="126" max="126"/>
-    <col width="32.28515625" customWidth="1" min="127" max="127"/>
-    <col width="32.28515625" customWidth="1" min="128" max="128"/>
-    <col width="32.28515625" customWidth="1" min="129" max="129"/>
-    <col width="32.28515625" customWidth="1" min="130" max="130"/>
-    <col width="32.28515625" customWidth="1" min="131" max="131"/>
-    <col width="32.28515625" customWidth="1" min="132" max="132"/>
-    <col width="32.28515625" customWidth="1" min="133" max="133"/>
-    <col width="32.28515625" customWidth="1" min="134" max="134"/>
-    <col width="32.28515625" customWidth="1" min="135" max="135"/>
-    <col width="32.28515625" customWidth="1" min="136" max="136"/>
-    <col width="32.28515625" customWidth="1" min="137" max="137"/>
-    <col width="32.28515625" customWidth="1" min="138" max="138"/>
-    <col width="32.28515625" customWidth="1" min="139" max="139"/>
-    <col width="32.28515625" customWidth="1" min="140" max="140"/>
-    <col width="32.28515625" customWidth="1" min="141" max="141"/>
-    <col width="32.28515625" customWidth="1" min="142" max="142"/>
-    <col width="32.28515625" customWidth="1" min="143" max="143"/>
-    <col width="32.28515625" customWidth="1" min="144" max="144"/>
-    <col width="32.28515625" customWidth="1" min="145" max="145"/>
-    <col width="32.28515625" customWidth="1" min="146" max="146"/>
-    <col width="32.28515625" customWidth="1" min="147" max="147"/>
-    <col width="32.28515625" customWidth="1" min="148" max="148"/>
-    <col width="32.28515625" customWidth="1" min="149" max="149"/>
-    <col width="32.28515625" customWidth="1" min="150" max="150"/>
-    <col width="32.28515625" customWidth="1" min="151" max="151"/>
-    <col width="32.28515625" customWidth="1" min="152" max="152"/>
-    <col width="32.28515625" customWidth="1" min="153" max="153"/>
-    <col width="32.28515625" customWidth="1" min="154" max="154"/>
-    <col width="32.28515625" customWidth="1" min="155" max="155"/>
-    <col width="32.28515625" customWidth="1" min="156" max="156"/>
-    <col width="32.28515625" customWidth="1" min="157" max="157"/>
-    <col width="32.28515625" customWidth="1" min="158" max="158"/>
-    <col width="32.28515625" customWidth="1" min="159" max="159"/>
-    <col width="32.28515625" customWidth="1" min="160" max="160"/>
-    <col width="32.28515625" customWidth="1" min="161" max="161"/>
-    <col width="32.28515625" customWidth="1" min="162" max="162"/>
-    <col width="32.28515625" customWidth="1" min="163" max="163"/>
-    <col width="32.28515625" customWidth="1" min="164" max="164"/>
-    <col width="32.28515625" customWidth="1" min="165" max="165"/>
-    <col width="32.28515625" customWidth="1" min="166" max="166"/>
-    <col width="32.28515625" customWidth="1" min="167" max="167"/>
-    <col width="32.28515625" customWidth="1" min="168" max="168"/>
-    <col width="32.28515625" customWidth="1" min="169" max="169"/>
-    <col width="32.28515625" customWidth="1" min="170" max="170"/>
-    <col width="32.28515625" customWidth="1" min="171" max="171"/>
-    <col width="32.28515625" customWidth="1" min="172" max="172"/>
-    <col width="32.28515625" customWidth="1" min="173" max="173"/>
-    <col width="32.28515625" customWidth="1" min="174" max="174"/>
-    <col width="32.28515625" customWidth="1" min="175" max="175"/>
-    <col width="32.28515625" customWidth="1" min="176" max="176"/>
-    <col width="32.28515625" customWidth="1" min="177" max="177"/>
-    <col width="32.28515625" customWidth="1" min="178" max="178"/>
-    <col width="32.28515625" customWidth="1" min="179" max="179"/>
-    <col width="32.28515625" customWidth="1" min="180" max="180"/>
-    <col width="32.28515625" customWidth="1" min="181" max="181"/>
-    <col width="32.28515625" customWidth="1" min="182" max="182"/>
-    <col width="32.28515625" customWidth="1" min="183" max="183"/>
-    <col width="32.28515625" customWidth="1" min="184" max="184"/>
-    <col width="32.28515625" customWidth="1" min="185" max="185"/>
-    <col width="32.28515625" customWidth="1" min="186" max="186"/>
-    <col width="32.28515625" customWidth="1" min="187" max="187"/>
-    <col width="32.28515625" customWidth="1" min="188" max="188"/>
-    <col width="32.28515625" customWidth="1" min="189" max="189"/>
-    <col width="32.28515625" customWidth="1" min="190" max="190"/>
-    <col width="32.28515625" customWidth="1" min="191" max="191"/>
-    <col width="32.28515625" customWidth="1" min="192" max="192"/>
-    <col width="32.28515625" customWidth="1" min="193" max="193"/>
-    <col width="32.28515625" customWidth="1" min="194" max="194"/>
-    <col width="32.28515625" customWidth="1" min="195" max="195"/>
-    <col width="32.28515625" customWidth="1" min="196" max="196"/>
-    <col width="32.28515625" customWidth="1" min="197" max="197"/>
-    <col width="32.28515625" customWidth="1" min="198" max="198"/>
-    <col width="32.28515625" customWidth="1" min="199" max="199"/>
-    <col width="32.28515625" customWidth="1" min="200" max="200"/>
-    <col width="32.28515625" customWidth="1" min="201" max="201"/>
-    <col width="32.28515625" customWidth="1" min="202" max="202"/>
-    <col width="32.28515625" customWidth="1" min="203" max="203"/>
-    <col width="32.28515625" customWidth="1" min="204" max="204"/>
-    <col width="32.28515625" customWidth="1" min="205" max="205"/>
-    <col width="32.28515625" customWidth="1" min="206" max="206"/>
-    <col width="32.28515625" customWidth="1" min="207" max="207"/>
-    <col width="32.28515625" customWidth="1" min="208" max="208"/>
-    <col width="32.28515625" customWidth="1" min="209" max="209"/>
-    <col width="32.28515625" customWidth="1" min="210" max="210"/>
-    <col width="32.28515625" customWidth="1" min="211" max="211"/>
-    <col width="32.28515625" customWidth="1" min="212" max="212"/>
-    <col width="32.28515625" customWidth="1" min="213" max="213"/>
-    <col width="32.28515625" customWidth="1" min="214" max="214"/>
-    <col width="32.28515625" customWidth="1" min="215" max="215"/>
-    <col width="32.28515625" customWidth="1" min="216" max="216"/>
-    <col width="32.28515625" customWidth="1" min="217" max="217"/>
-    <col width="32.28515625" customWidth="1" min="218" max="218"/>
-    <col width="32.28515625" customWidth="1" min="219" max="219"/>
-    <col width="32.28515625" customWidth="1" min="220" max="220"/>
-    <col width="32.28515625" customWidth="1" min="221" max="221"/>
-    <col width="32.28515625" customWidth="1" min="222" max="222"/>
-    <col width="32.28515625" customWidth="1" min="223" max="223"/>
-    <col width="32.28515625" customWidth="1" min="224" max="224"/>
-    <col width="32.28515625" customWidth="1" min="225" max="225"/>
-    <col width="32.28515625" customWidth="1" min="226" max="226"/>
-    <col width="32.28515625" customWidth="1" min="227" max="227"/>
-    <col width="32.28515625" customWidth="1" min="228" max="228"/>
-    <col width="32.28515625" customWidth="1" min="229" max="229"/>
-    <col width="32.28515625" customWidth="1" min="230" max="230"/>
-    <col width="32.28515625" customWidth="1" min="231" max="231"/>
-    <col width="32.28515625" customWidth="1" min="232" max="232"/>
-    <col width="32.28515625" customWidth="1" min="233" max="233"/>
-    <col width="32.28515625" customWidth="1" min="234" max="234"/>
-    <col width="32.28515625" customWidth="1" min="235" max="235"/>
-    <col width="32.28515625" customWidth="1" min="236" max="236"/>
-    <col width="32.28515625" customWidth="1" min="237" max="237"/>
-    <col width="32.28515625" customWidth="1" min="238" max="238"/>
-    <col width="32.28515625" customWidth="1" min="239" max="239"/>
-    <col width="32.28515625" customWidth="1" min="240" max="240"/>
-    <col width="32.28515625" customWidth="1" min="241" max="241"/>
-    <col width="32.28515625" customWidth="1" min="242" max="242"/>
-    <col width="32.28515625" customWidth="1" min="243" max="243"/>
-    <col width="32.28515625" customWidth="1" min="244" max="244"/>
-    <col width="32.28515625" customWidth="1" min="245" max="245"/>
-    <col width="32.28515625" customWidth="1" min="246" max="246"/>
-    <col width="32.28515625" customWidth="1" min="247" max="247"/>
-    <col width="32.28515625" customWidth="1" min="248" max="248"/>
-    <col width="32.28515625" customWidth="1" min="249" max="249"/>
-    <col width="32.28515625" customWidth="1" min="250" max="250"/>
-    <col width="32.28515625" customWidth="1" min="251" max="251"/>
-    <col width="32.28515625" customWidth="1" min="252" max="252"/>
-    <col width="32.28515625" customWidth="1" min="253" max="253"/>
-    <col width="32.28515625" customWidth="1" min="254" max="254"/>
-    <col width="32.28515625" customWidth="1" min="255" max="255"/>
-    <col width="32.28515625" customWidth="1" min="256" max="256"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="22" customWidth="1" min="53" max="53"/>
+    <col width="16" customWidth="1" min="54" max="54"/>
+    <col width="19.5703125" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
+    <col width="21.140625" customWidth="1" min="57" max="57"/>
+    <col width="16" customWidth="1" min="58" max="58"/>
+    <col width="18.85546875" customWidth="1" min="59" max="59"/>
+    <col width="20.5703125" customWidth="1" min="60" max="60"/>
+    <col width="21" customWidth="1" min="61" max="61"/>
+    <col width="16" customWidth="1" min="62" max="62"/>
+    <col width="25.5703125" customWidth="1" min="63" max="63"/>
+    <col width="23.42578125" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="21.5703125" customWidth="1" min="66" max="66"/>
+    <col width="18.7109375" customWidth="1" min="67" max="67"/>
+    <col width="19.7109375" customWidth="1" min="68" max="68"/>
+    <col width="28" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Customer Number</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Policy Insured Name</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Claim Number</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Claimant Name - Company</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Account Location Identifier</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>Accident State</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>Policy Symbol</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>Policy Number</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>Policy MOD</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
+        <is>
+          <t>Policy Effective Date</t>
+        </is>
+      </c>
+      <c r="L1" s="25" t="inlineStr">
+        <is>
+          <t>Policy Expiration Date</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t>Producing Agent Code</t>
+        </is>
+      </c>
+      <c r="N1" s="25" t="inlineStr">
+        <is>
+          <t>Loss Date</t>
+        </is>
+      </c>
+      <c r="O1" s="25" t="inlineStr">
+        <is>
+          <t>Date of Notice (Report Date)</t>
+        </is>
+      </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>Lag Time</t>
+        </is>
+      </c>
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>Claim Status</t>
+        </is>
+      </c>
+      <c r="R1" s="25" t="inlineStr">
+        <is>
+          <t>Claim Closed Date</t>
+        </is>
+      </c>
+      <c r="S1" s="23" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="T1" s="26" t="inlineStr">
+        <is>
+          <t>Current Loss Reserve</t>
+        </is>
+      </c>
+      <c r="U1" s="26" t="inlineStr">
+        <is>
+          <t>Paid Loss Net Salvage Subro</t>
+        </is>
+      </c>
+      <c r="V1" s="26" t="inlineStr">
+        <is>
+          <t>Total Incurred</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Claims above 25K</t>
+        </is>
+      </c>
+      <c r="X1" s="26" t="inlineStr">
+        <is>
+          <t>Total Expense</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Salvage Recovery</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Subro Recovery</t>
+        </is>
+      </c>
+      <c r="AA1" s="27" t="inlineStr">
+        <is>
+          <t>Loss Recovery</t>
+        </is>
+      </c>
+      <c r="AB1" s="27" t="inlineStr">
+        <is>
+          <t>Deductible Recovery</t>
+        </is>
+      </c>
+      <c r="AC1" s="27" t="inlineStr">
+        <is>
+          <t>Recoveries</t>
+        </is>
+      </c>
+      <c r="AD1" s="27" t="inlineStr">
+        <is>
+          <t>Total ALAE Amount</t>
+        </is>
+      </c>
+      <c r="AE1" s="27" t="inlineStr">
+        <is>
+          <t>Expense Column</t>
+        </is>
+      </c>
+      <c r="AF1" s="27" t="inlineStr">
+        <is>
+          <t>Expense TXN</t>
+        </is>
+      </c>
+      <c r="AG1" s="27" t="inlineStr">
+        <is>
+          <t>Expense Recovery TXN</t>
+        </is>
+      </c>
+      <c r="AH1" s="27" t="inlineStr">
+        <is>
+          <t>Expense_Recovery</t>
+        </is>
+      </c>
+      <c r="AI1" s="23" t="inlineStr">
+        <is>
+          <t>Cause Of Loss</t>
+        </is>
+      </c>
+      <c r="AJ1" s="23" t="inlineStr">
+        <is>
+          <t>Description Of Loss</t>
+        </is>
+      </c>
+      <c r="AK1" s="23" t="inlineStr">
+        <is>
+          <t>Contributing Factor</t>
+        </is>
+      </c>
+      <c r="AL1" s="28" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Effective Date_Source</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Effective Date</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="AM1" s="23" t="inlineStr">
         <is>
           <t>Policy Year</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Expiration Date_Source</t>
-        </is>
-      </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="AN1" s="28" t="inlineStr">
         <is>
           <t>Policy Holder Claim Number</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Expiration Date</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>Producing Agent Code</t>
-        </is>
-      </c>
-      <c r="O1" s="11" t="inlineStr">
+      <c r="AO1" s="28" t="inlineStr">
         <is>
           <t>Producing Agent Name</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>Claim Number</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>Feature Number</t>
-        </is>
-      </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="AP1" s="28" t="inlineStr">
         <is>
           <t>Claim Feature Number</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="T1" s="12" t="inlineStr">
-        <is>
-          <t>Loss Date_Source</t>
-        </is>
-      </c>
-      <c r="U1" s="12" t="inlineStr">
-        <is>
-          <t>Loss Date</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>Accident State</t>
-        </is>
-      </c>
-      <c r="W1" s="13" t="inlineStr">
-        <is>
-          <t>Current Loss Reserve</t>
-        </is>
-      </c>
-      <c r="X1" s="13" t="inlineStr">
-        <is>
-          <t>Paid Loss Net Salvage Subro</t>
-        </is>
-      </c>
-      <c r="Y1" s="13" t="inlineStr">
-        <is>
-          <t>Total Incurred</t>
-        </is>
-      </c>
-      <c r="Z1" s="14" t="inlineStr">
-        <is>
-          <t>Claims above 25K</t>
-        </is>
-      </c>
-      <c r="AA1" s="13" t="inlineStr">
-        <is>
-          <t>Total Expense</t>
-        </is>
-      </c>
-      <c r="AB1" s="14" t="inlineStr">
-        <is>
-          <t>Salvage Recovery</t>
-        </is>
-      </c>
-      <c r="AC1" s="14" t="inlineStr">
-        <is>
-          <t>Subro Recovery</t>
-        </is>
-      </c>
-      <c r="AD1" s="14" t="inlineStr">
-        <is>
-          <t>Loss Recovery</t>
-        </is>
-      </c>
-      <c r="AE1" s="14" t="inlineStr">
-        <is>
-          <t>Deductible Recovery</t>
-        </is>
-      </c>
-      <c r="AF1" s="14" t="inlineStr">
-        <is>
-          <t>Recoveries</t>
-        </is>
-      </c>
-      <c r="AG1" s="14" t="inlineStr">
-        <is>
-          <t>Total ALAE Amount</t>
-        </is>
-      </c>
-      <c r="AH1" s="14" t="inlineStr">
-        <is>
-          <t>Expense Column</t>
-        </is>
-      </c>
-      <c r="AI1" s="14" t="inlineStr">
-        <is>
-          <t>Expense TXN</t>
-        </is>
-      </c>
-      <c r="AJ1" s="14" t="inlineStr">
-        <is>
-          <t>Expense Recovery TXN</t>
-        </is>
-      </c>
-      <c r="AK1" s="14" t="inlineStr">
-        <is>
-          <t>Expense_Recovery</t>
-        </is>
-      </c>
-      <c r="AL1" s="11" t="inlineStr">
+      <c r="AQ1" s="28" t="inlineStr">
         <is>
           <t>Litigation Status</t>
         </is>
       </c>
-      <c r="AM1" s="9" t="inlineStr">
-        <is>
-          <t>Cause Of Loss</t>
-        </is>
-      </c>
-      <c r="AN1" s="9" t="inlineStr">
-        <is>
-          <t>Description Of Loss</t>
-        </is>
-      </c>
-      <c r="AO1" s="9" t="inlineStr">
-        <is>
-          <t>Contributing Factor</t>
-        </is>
-      </c>
-      <c r="AP1" s="11" t="inlineStr">
+      <c r="AR1" s="28" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AS1" s="28" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="AR1" s="11" t="inlineStr">
+      <c r="AT1" s="28" t="inlineStr">
         <is>
           <t>Policy Region Description</t>
         </is>
       </c>
-      <c r="AS1" s="11" t="inlineStr">
+      <c r="AU1" s="28" t="inlineStr">
         <is>
           <t>Policy Holder Retailer Desc</t>
         </is>
       </c>
-      <c r="AT1" s="12" t="inlineStr">
-        <is>
-          <t>Reported Date_Source</t>
-        </is>
-      </c>
-      <c r="AU1" s="12" t="inlineStr">
-        <is>
-          <t>Reported Date</t>
-        </is>
-      </c>
-      <c r="AV1" s="9" t="inlineStr">
-        <is>
-          <t>Claim Status</t>
-        </is>
-      </c>
-      <c r="AW1" s="12" t="inlineStr">
-        <is>
-          <t>Claim Closed Date_Source</t>
-        </is>
-      </c>
-      <c r="AX1" s="12" t="inlineStr">
-        <is>
-          <t>Claim Closed Date</t>
-        </is>
-      </c>
-      <c r="AY1" s="9" t="inlineStr">
-        <is>
-          <t>Claimant Name - Company</t>
-        </is>
-      </c>
-      <c r="AZ1" s="11" t="inlineStr">
+      <c r="AV1" s="28" t="inlineStr">
         <is>
           <t>CLMNT_FIRST_NM</t>
         </is>
       </c>
-      <c r="BA1" s="11" t="inlineStr">
+      <c r="AW1" s="28" t="inlineStr">
         <is>
           <t>CLMNT_LAST_NM</t>
         </is>
       </c>
-      <c r="BB1" s="11" t="inlineStr">
+      <c r="AX1" s="28" t="inlineStr">
         <is>
           <t>CLMNT_FULL_NM</t>
         </is>
       </c>
-      <c r="BC1" s="11" t="inlineStr">
+      <c r="AY1" s="28" t="inlineStr">
         <is>
           <t>CLMNT_CO_NM</t>
         </is>
       </c>
-      <c r="BD1" s="11" t="inlineStr">
+      <c r="AZ1" s="28" t="inlineStr">
         <is>
           <t>Occupation</t>
         </is>
       </c>
-      <c r="BE1" s="11" t="inlineStr">
+      <c r="BA1" s="28" t="inlineStr">
         <is>
           <t>Accident Day Of Week</t>
         </is>
       </c>
-      <c r="BF1" s="11" t="inlineStr">
+      <c r="BB1" s="28" t="inlineStr">
         <is>
           <t>Insured Driver</t>
         </is>
       </c>
-      <c r="BG1" s="11" t="inlineStr">
+      <c r="BC1" s="28" t="inlineStr">
         <is>
           <t>Total Loss Indicator</t>
         </is>
       </c>
-      <c r="BH1" s="11" t="inlineStr">
+      <c r="BD1" s="28" t="inlineStr">
         <is>
           <t>Vehicle Year</t>
         </is>
       </c>
-      <c r="BI1" s="11" t="inlineStr">
+      <c r="BE1" s="28" t="inlineStr">
         <is>
           <t>Vehicle Manufacturer</t>
         </is>
       </c>
-      <c r="BJ1" s="11" t="inlineStr">
+      <c r="BF1" s="28" t="inlineStr">
         <is>
           <t>Vehicle Model</t>
         </is>
       </c>
-      <c r="BK1" s="11" t="inlineStr">
+      <c r="BG1" s="28" t="inlineStr">
         <is>
           <t>Vehicle ID Number</t>
         </is>
       </c>
-      <c r="BL1" s="11" t="inlineStr">
+      <c r="BH1" s="28" t="inlineStr">
         <is>
           <t>Vehicle License Plate</t>
         </is>
       </c>
-      <c r="BM1" s="11" t="inlineStr">
+      <c r="BI1" s="28" t="inlineStr">
         <is>
           <t>Vehicle License State</t>
         </is>
       </c>
-      <c r="BN1" s="11" t="inlineStr">
+      <c r="BJ1" s="28" t="inlineStr">
         <is>
           <t>Adjuster</t>
         </is>
       </c>
-      <c r="BO1" s="11" t="inlineStr">
+      <c r="BK1" s="28" t="inlineStr">
         <is>
           <t>Adjuster Email</t>
         </is>
       </c>
-      <c r="BP1" s="11" t="inlineStr">
+      <c r="BL1" s="28" t="inlineStr">
         <is>
           <t>Adjuster Phone Number</t>
         </is>
       </c>
-      <c r="BQ1" s="11" t="inlineStr">
+      <c r="BM1" s="28" t="inlineStr">
         <is>
           <t>Record Source Code</t>
         </is>
       </c>
-      <c r="BR1" s="11" t="inlineStr">
+      <c r="BN1" s="28" t="inlineStr">
         <is>
           <t>Record Only Indicator</t>
         </is>
       </c>
-      <c r="BS1" s="11" t="inlineStr">
+      <c r="BO1" s="28" t="inlineStr">
         <is>
           <t>Exposure Indicator</t>
         </is>
       </c>
-      <c r="BT1" s="11" t="inlineStr">
+      <c r="BP1" s="28" t="inlineStr">
         <is>
           <t>Current Version IND</t>
         </is>
       </c>
-      <c r="BU1" s="11" t="inlineStr">
+      <c r="BQ1" s="28" t="inlineStr">
         <is>
           <t>System Date</t>
         </is>
@@ -1638,29 +1498,32 @@
       <c r="B2" s="15" t="n"/>
       <c r="C2" s="15" t="n"/>
       <c r="D2" s="15" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="17" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
       <c r="G2" s="15" t="n"/>
-      <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
-      <c r="J2" s="15" t="n"/>
-      <c r="K2" s="18" t="n"/>
-      <c r="L2" s="15" t="n"/>
-      <c r="M2" s="18" t="n"/>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="15" t="n"/>
-      <c r="P2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="29" t="n"/>
+      <c r="L2" s="29" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="29" t="n"/>
+      <c r="O2" s="29" t="n"/>
+      <c r="P2" s="30">
+        <f>IF(OR(N2="",O2=""),"",INT(O2)-INT(N2))</f>
+        <v/>
+      </c>
       <c r="Q2" s="15" t="n"/>
-      <c r="R2" s="15" t="n"/>
+      <c r="R2" s="29" t="n"/>
       <c r="S2" s="15" t="n"/>
-      <c r="T2" s="18" t="n"/>
-      <c r="U2" s="18" t="n"/>
-      <c r="V2" s="15" t="n"/>
+      <c r="T2" s="19" t="n"/>
+      <c r="U2" s="19" t="n"/>
+      <c r="V2" s="19" t="n"/>
       <c r="W2" s="19" t="n"/>
       <c r="X2" s="19" t="n"/>
-      <c r="Y2" s="19" t="n"/>
-      <c r="Z2" s="19" t="n"/>
-      <c r="AA2" s="19" t="n"/>
+      <c r="Y2" s="20" t="n"/>
+      <c r="Z2" s="20" t="n"/>
+      <c r="AA2" s="20" t="n"/>
       <c r="AB2" s="20" t="n"/>
       <c r="AC2" s="20" t="n"/>
       <c r="AD2" s="20" t="n"/>
@@ -1668,9 +1531,9 @@
       <c r="AF2" s="20" t="n"/>
       <c r="AG2" s="20" t="n"/>
       <c r="AH2" s="20" t="n"/>
-      <c r="AI2" s="20" t="n"/>
-      <c r="AJ2" s="20" t="n"/>
-      <c r="AK2" s="20" t="n"/>
+      <c r="AI2" s="15" t="n"/>
+      <c r="AJ2" s="15" t="n"/>
+      <c r="AK2" s="15" t="n"/>
       <c r="AL2" s="15" t="n"/>
       <c r="AM2" s="15" t="n"/>
       <c r="AN2" s="15" t="n"/>
@@ -1679,11 +1542,11 @@
       <c r="AQ2" s="15" t="n"/>
       <c r="AR2" s="15" t="n"/>
       <c r="AS2" s="15" t="n"/>
-      <c r="AT2" s="18" t="n"/>
-      <c r="AU2" s="18" t="n"/>
+      <c r="AT2" s="15" t="n"/>
+      <c r="AU2" s="15" t="n"/>
       <c r="AV2" s="15" t="n"/>
-      <c r="AW2" s="18" t="n"/>
-      <c r="AX2" s="18" t="n"/>
+      <c r="AW2" s="15" t="n"/>
+      <c r="AX2" s="15" t="n"/>
       <c r="AY2" s="15" t="n"/>
       <c r="AZ2" s="15" t="n"/>
       <c r="BA2" s="15" t="n"/>
@@ -1703,14 +1566,11 @@
       <c r="BO2" s="15" t="n"/>
       <c r="BP2" s="15" t="n"/>
       <c r="BQ2" s="15" t="n"/>
-      <c r="BR2" s="15" t="n"/>
-      <c r="BS2" s="15" t="n"/>
-      <c r="BT2" s="15" t="n"/>
-      <c r="BU2" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU2"/>
+  <autoFilter ref="A1:BQ2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1720,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -1729,455 +1589,221 @@
     <col width="33.28515625" customWidth="1" min="4" max="4"/>
     <col width="33.28515625" customWidth="1" min="5" max="5"/>
     <col width="33.28515625" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="33.28515625" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="10" max="10"/>
+    <col width="33.28515625" customWidth="1" min="9" max="9"/>
+    <col width="33.28515625" customWidth="1" min="10" max="10"/>
     <col width="33.28515625" customWidth="1" min="11" max="11"/>
     <col width="33.28515625" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="13" max="13"/>
+    <col width="33.28515625" customWidth="1" min="13" max="13"/>
     <col width="33.28515625" customWidth="1" min="14" max="14"/>
     <col width="33.28515625" customWidth="1" min="15" max="15"/>
-    <col width="33.28515625" customWidth="1" min="16" max="16"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="33.28515625" customWidth="1" min="17" max="17"/>
     <col width="33.28515625" customWidth="1" min="18" max="18"/>
     <col width="33.28515625" customWidth="1" min="19" max="19"/>
     <col width="33.28515625" customWidth="1" min="20" max="20"/>
     <col width="33.28515625" customWidth="1" min="21" max="21"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="26" max="26"/>
+    <col width="33.28515625" customWidth="1" min="22" max="22"/>
+    <col width="33.28515625" customWidth="1" min="23" max="23"/>
+    <col width="33.28515625" customWidth="1" min="24" max="24"/>
+    <col width="33.28515625" customWidth="1" min="25" max="25"/>
+    <col width="33.28515625" customWidth="1" min="26" max="26"/>
     <col width="33.28515625" customWidth="1" min="27" max="27"/>
     <col width="33.28515625" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="30" max="30"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="31" max="31"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="32" max="32"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="33" max="33"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="36" max="36"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="37" max="37"/>
-    <col width="33.28515625" customWidth="1" min="38" max="38"/>
-    <col width="33.28515625" customWidth="1" min="39" max="39"/>
-    <col hidden="1" width="33.28515625" customWidth="1" min="40" max="40"/>
-    <col width="33.28515625" customWidth="1" min="41" max="41"/>
-    <col width="33.28515625" customWidth="1" min="42" max="42"/>
-    <col width="33.28515625" customWidth="1" min="43" max="43"/>
-    <col width="33.28515625" customWidth="1" min="44" max="44"/>
-    <col width="33.28515625" customWidth="1" min="45" max="45"/>
-    <col width="33.28515625" customWidth="1" min="46" max="46"/>
-    <col width="33.28515625" customWidth="1" min="47" max="47"/>
-    <col width="33.28515625" customWidth="1" min="48" max="48"/>
-    <col width="33.28515625" customWidth="1" min="49" max="49"/>
-    <col width="33.28515625" customWidth="1" min="50" max="50"/>
-    <col width="33.28515625" customWidth="1" min="51" max="51"/>
-    <col width="33.28515625" customWidth="1" min="52" max="52"/>
-    <col width="33.28515625" customWidth="1" min="53" max="53"/>
-    <col width="33.28515625" customWidth="1" min="54" max="54"/>
-    <col width="33.28515625" customWidth="1" min="55" max="55"/>
-    <col width="33.28515625" customWidth="1" min="56" max="56"/>
-    <col width="33.28515625" customWidth="1" min="57" max="57"/>
-    <col width="33.28515625" customWidth="1" min="58" max="58"/>
-    <col width="33.28515625" customWidth="1" min="59" max="59"/>
-    <col width="33.28515625" customWidth="1" min="60" max="60"/>
-    <col width="33.28515625" customWidth="1" min="61" max="61"/>
-    <col width="33.28515625" customWidth="1" min="62" max="62"/>
-    <col width="33.28515625" customWidth="1" min="63" max="63"/>
-    <col width="33.28515625" customWidth="1" min="64" max="64"/>
-    <col width="33.28515625" customWidth="1" min="65" max="65"/>
-    <col width="33.28515625" customWidth="1" min="66" max="66"/>
-    <col width="33.28515625" customWidth="1" min="67" max="67"/>
-    <col width="33.28515625" customWidth="1" min="68" max="68"/>
-    <col width="33.28515625" customWidth="1" min="69" max="69"/>
-    <col width="33.28515625" customWidth="1" min="70" max="70"/>
-    <col width="33.28515625" customWidth="1" min="71" max="71"/>
-    <col width="33.28515625" customWidth="1" min="72" max="72"/>
-    <col width="33.28515625" customWidth="1" min="73" max="73"/>
-    <col width="33.28515625" customWidth="1" min="74" max="74"/>
-    <col width="33.28515625" customWidth="1" min="75" max="75"/>
-    <col width="33.28515625" customWidth="1" min="76" max="76"/>
-    <col width="33.28515625" customWidth="1" min="77" max="77"/>
-    <col width="33.28515625" customWidth="1" min="78" max="78"/>
-    <col width="33.28515625" customWidth="1" min="79" max="79"/>
-    <col width="33.28515625" customWidth="1" min="80" max="80"/>
-    <col width="33.28515625" customWidth="1" min="81" max="81"/>
-    <col width="33.28515625" customWidth="1" min="82" max="82"/>
-    <col width="33.28515625" customWidth="1" min="83" max="83"/>
-    <col width="33.28515625" customWidth="1" min="84" max="84"/>
-    <col width="33.28515625" customWidth="1" min="85" max="85"/>
-    <col width="33.28515625" customWidth="1" min="86" max="86"/>
-    <col width="33.28515625" customWidth="1" min="87" max="87"/>
-    <col width="33.28515625" customWidth="1" min="88" max="88"/>
-    <col width="33.28515625" customWidth="1" min="89" max="89"/>
-    <col width="33.28515625" customWidth="1" min="90" max="90"/>
-    <col width="33.28515625" customWidth="1" min="91" max="91"/>
-    <col width="33.28515625" customWidth="1" min="92" max="92"/>
-    <col width="33.28515625" customWidth="1" min="93" max="93"/>
-    <col width="33.28515625" customWidth="1" min="94" max="94"/>
-    <col width="33.28515625" customWidth="1" min="95" max="95"/>
-    <col width="33.28515625" customWidth="1" min="96" max="96"/>
-    <col width="33.28515625" customWidth="1" min="97" max="97"/>
-    <col width="33.28515625" customWidth="1" min="98" max="98"/>
-    <col width="33.28515625" customWidth="1" min="99" max="99"/>
-    <col width="33.28515625" customWidth="1" min="100" max="100"/>
-    <col width="33.28515625" customWidth="1" min="101" max="101"/>
-    <col width="33.28515625" customWidth="1" min="102" max="102"/>
-    <col width="33.28515625" customWidth="1" min="103" max="103"/>
-    <col width="33.28515625" customWidth="1" min="104" max="104"/>
-    <col width="33.28515625" customWidth="1" min="105" max="105"/>
-    <col width="33.28515625" customWidth="1" min="106" max="106"/>
-    <col width="33.28515625" customWidth="1" min="107" max="107"/>
-    <col width="33.28515625" customWidth="1" min="108" max="108"/>
-    <col width="33.28515625" customWidth="1" min="109" max="109"/>
-    <col width="33.28515625" customWidth="1" min="110" max="110"/>
-    <col width="33.28515625" customWidth="1" min="111" max="111"/>
-    <col width="33.28515625" customWidth="1" min="112" max="112"/>
-    <col width="33.28515625" customWidth="1" min="113" max="113"/>
-    <col width="33.28515625" customWidth="1" min="114" max="114"/>
-    <col width="33.28515625" customWidth="1" min="115" max="115"/>
-    <col width="33.28515625" customWidth="1" min="116" max="116"/>
-    <col width="33.28515625" customWidth="1" min="117" max="117"/>
-    <col width="33.28515625" customWidth="1" min="118" max="118"/>
-    <col width="33.28515625" customWidth="1" min="119" max="119"/>
-    <col width="33.28515625" customWidth="1" min="120" max="120"/>
-    <col width="33.28515625" customWidth="1" min="121" max="121"/>
-    <col width="33.28515625" customWidth="1" min="122" max="122"/>
-    <col width="33.28515625" customWidth="1" min="123" max="123"/>
-    <col width="33.28515625" customWidth="1" min="124" max="124"/>
-    <col width="33.28515625" customWidth="1" min="125" max="125"/>
-    <col width="33.28515625" customWidth="1" min="126" max="126"/>
-    <col width="33.28515625" customWidth="1" min="127" max="127"/>
-    <col width="33.28515625" customWidth="1" min="128" max="128"/>
-    <col width="33.28515625" customWidth="1" min="129" max="129"/>
-    <col width="33.28515625" customWidth="1" min="130" max="130"/>
-    <col width="33.28515625" customWidth="1" min="131" max="131"/>
-    <col width="33.28515625" customWidth="1" min="132" max="132"/>
-    <col width="33.28515625" customWidth="1" min="133" max="133"/>
-    <col width="33.28515625" customWidth="1" min="134" max="134"/>
-    <col width="33.28515625" customWidth="1" min="135" max="135"/>
-    <col width="33.28515625" customWidth="1" min="136" max="136"/>
-    <col width="33.28515625" customWidth="1" min="137" max="137"/>
-    <col width="33.28515625" customWidth="1" min="138" max="138"/>
-    <col width="33.28515625" customWidth="1" min="139" max="139"/>
-    <col width="33.28515625" customWidth="1" min="140" max="140"/>
-    <col width="33.28515625" customWidth="1" min="141" max="141"/>
-    <col width="33.28515625" customWidth="1" min="142" max="142"/>
-    <col width="33.28515625" customWidth="1" min="143" max="143"/>
-    <col width="33.28515625" customWidth="1" min="144" max="144"/>
-    <col width="33.28515625" customWidth="1" min="145" max="145"/>
-    <col width="33.28515625" customWidth="1" min="146" max="146"/>
-    <col width="33.28515625" customWidth="1" min="147" max="147"/>
-    <col width="33.28515625" customWidth="1" min="148" max="148"/>
-    <col width="33.28515625" customWidth="1" min="149" max="149"/>
-    <col width="33.28515625" customWidth="1" min="150" max="150"/>
-    <col width="33.28515625" customWidth="1" min="151" max="151"/>
-    <col width="33.28515625" customWidth="1" min="152" max="152"/>
-    <col width="33.28515625" customWidth="1" min="153" max="153"/>
-    <col width="33.28515625" customWidth="1" min="154" max="154"/>
-    <col width="33.28515625" customWidth="1" min="155" max="155"/>
-    <col width="33.28515625" customWidth="1" min="156" max="156"/>
-    <col width="33.28515625" customWidth="1" min="157" max="157"/>
-    <col width="33.28515625" customWidth="1" min="158" max="158"/>
-    <col width="33.28515625" customWidth="1" min="159" max="159"/>
-    <col width="33.28515625" customWidth="1" min="160" max="160"/>
-    <col width="33.28515625" customWidth="1" min="161" max="161"/>
-    <col width="33.28515625" customWidth="1" min="162" max="162"/>
-    <col width="33.28515625" customWidth="1" min="163" max="163"/>
-    <col width="33.28515625" customWidth="1" min="164" max="164"/>
-    <col width="33.28515625" customWidth="1" min="165" max="165"/>
-    <col width="33.28515625" customWidth="1" min="166" max="166"/>
-    <col width="33.28515625" customWidth="1" min="167" max="167"/>
-    <col width="33.28515625" customWidth="1" min="168" max="168"/>
-    <col width="33.28515625" customWidth="1" min="169" max="169"/>
-    <col width="33.28515625" customWidth="1" min="170" max="170"/>
-    <col width="33.28515625" customWidth="1" min="171" max="171"/>
-    <col width="33.28515625" customWidth="1" min="172" max="172"/>
-    <col width="33.28515625" customWidth="1" min="173" max="173"/>
-    <col width="33.28515625" customWidth="1" min="174" max="174"/>
-    <col width="33.28515625" customWidth="1" min="175" max="175"/>
-    <col width="33.28515625" customWidth="1" min="176" max="176"/>
-    <col width="33.28515625" customWidth="1" min="177" max="177"/>
-    <col width="33.28515625" customWidth="1" min="178" max="178"/>
-    <col width="33.28515625" customWidth="1" min="179" max="179"/>
-    <col width="33.28515625" customWidth="1" min="180" max="180"/>
-    <col width="33.28515625" customWidth="1" min="181" max="181"/>
-    <col width="33.28515625" customWidth="1" min="182" max="182"/>
-    <col width="33.28515625" customWidth="1" min="183" max="183"/>
-    <col width="33.28515625" customWidth="1" min="184" max="184"/>
-    <col width="33.28515625" customWidth="1" min="185" max="185"/>
-    <col width="33.28515625" customWidth="1" min="186" max="186"/>
-    <col width="33.28515625" customWidth="1" min="187" max="187"/>
-    <col width="33.28515625" customWidth="1" min="188" max="188"/>
-    <col width="33.28515625" customWidth="1" min="189" max="189"/>
-    <col width="33.28515625" customWidth="1" min="190" max="190"/>
-    <col width="33.28515625" customWidth="1" min="191" max="191"/>
-    <col width="33.28515625" customWidth="1" min="192" max="192"/>
-    <col width="33.28515625" customWidth="1" min="193" max="193"/>
-    <col width="33.28515625" customWidth="1" min="194" max="194"/>
-    <col width="33.28515625" customWidth="1" min="195" max="195"/>
-    <col width="33.28515625" customWidth="1" min="196" max="196"/>
-    <col width="33.28515625" customWidth="1" min="197" max="197"/>
-    <col width="33.28515625" customWidth="1" min="198" max="198"/>
-    <col width="33.28515625" customWidth="1" min="199" max="199"/>
-    <col width="33.28515625" customWidth="1" min="200" max="200"/>
-    <col width="33.28515625" customWidth="1" min="201" max="201"/>
-    <col width="33.28515625" customWidth="1" min="202" max="202"/>
-    <col width="33.28515625" customWidth="1" min="203" max="203"/>
-    <col width="33.28515625" customWidth="1" min="204" max="204"/>
-    <col width="33.28515625" customWidth="1" min="205" max="205"/>
-    <col width="33.28515625" customWidth="1" min="206" max="206"/>
-    <col width="33.28515625" customWidth="1" min="207" max="207"/>
-    <col width="33.28515625" customWidth="1" min="208" max="208"/>
-    <col width="33.28515625" customWidth="1" min="209" max="209"/>
-    <col width="33.28515625" customWidth="1" min="210" max="210"/>
-    <col width="33.28515625" customWidth="1" min="211" max="211"/>
-    <col width="33.28515625" customWidth="1" min="212" max="212"/>
-    <col width="33.28515625" customWidth="1" min="213" max="213"/>
-    <col width="33.28515625" customWidth="1" min="214" max="214"/>
-    <col width="33.28515625" customWidth="1" min="215" max="215"/>
-    <col width="33.28515625" customWidth="1" min="216" max="216"/>
-    <col width="33.28515625" customWidth="1" min="217" max="217"/>
-    <col width="33.28515625" customWidth="1" min="218" max="218"/>
-    <col width="33.28515625" customWidth="1" min="219" max="219"/>
-    <col width="33.28515625" customWidth="1" min="220" max="220"/>
-    <col width="33.28515625" customWidth="1" min="221" max="221"/>
-    <col width="33.28515625" customWidth="1" min="222" max="222"/>
-    <col width="33.28515625" customWidth="1" min="223" max="223"/>
-    <col width="33.28515625" customWidth="1" min="224" max="224"/>
-    <col width="33.28515625" customWidth="1" min="225" max="225"/>
-    <col width="33.28515625" customWidth="1" min="226" max="226"/>
-    <col width="33.28515625" customWidth="1" min="227" max="227"/>
-    <col width="33.28515625" customWidth="1" min="228" max="228"/>
-    <col width="33.28515625" customWidth="1" min="229" max="229"/>
-    <col width="33.28515625" customWidth="1" min="230" max="230"/>
-    <col width="33.28515625" customWidth="1" min="231" max="231"/>
-    <col width="33.28515625" customWidth="1" min="232" max="232"/>
-    <col width="33.28515625" customWidth="1" min="233" max="233"/>
-    <col width="33.28515625" customWidth="1" min="234" max="234"/>
-    <col width="33.28515625" customWidth="1" min="235" max="235"/>
-    <col width="33.28515625" customWidth="1" min="236" max="236"/>
-    <col width="33.28515625" customWidth="1" min="237" max="237"/>
-    <col width="33.28515625" customWidth="1" min="238" max="238"/>
-    <col width="33.28515625" customWidth="1" min="239" max="239"/>
-    <col width="33.28515625" customWidth="1" min="240" max="240"/>
-    <col width="33.28515625" customWidth="1" min="241" max="241"/>
-    <col width="33.28515625" customWidth="1" min="242" max="242"/>
-    <col width="33.28515625" customWidth="1" min="243" max="243"/>
-    <col width="33.28515625" customWidth="1" min="244" max="244"/>
-    <col width="33.28515625" customWidth="1" min="245" max="245"/>
-    <col width="33.28515625" customWidth="1" min="246" max="246"/>
-    <col width="33.28515625" customWidth="1" min="247" max="247"/>
-    <col width="33.28515625" customWidth="1" min="248" max="248"/>
-    <col width="33.28515625" customWidth="1" min="249" max="249"/>
-    <col width="33.28515625" customWidth="1" min="250" max="250"/>
-    <col width="33.28515625" customWidth="1" min="251" max="251"/>
-    <col width="33.28515625" customWidth="1" min="252" max="252"/>
-    <col width="33.28515625" customWidth="1" min="253" max="253"/>
-    <col width="33.28515625" customWidth="1" min="254" max="254"/>
-    <col width="33.28515625" customWidth="1" min="255" max="255"/>
-    <col width="33.28515625" customWidth="1" min="256" max="256"/>
+    <col width="33.28515625" customWidth="1" min="29" max="29"/>
+    <col width="33.28515625" customWidth="1" min="30" max="30"/>
+    <col width="33.28515625" customWidth="1" min="31" max="31"/>
+    <col width="33.28515625" customWidth="1" min="32" max="32"/>
+    <col width="33.28515625" customWidth="1" min="33" max="33"/>
+    <col width="33.28515625" customWidth="1" min="34" max="34"/>
+    <col width="33.28515625" customWidth="1" min="35" max="35"/>
+    <col width="33.28515625" customWidth="1" min="36" max="36"/>
+    <col width="33.28515625" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Customer Number</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Policy Insured Name</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Claim Number</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Claimant Name - Company</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Account Location Identifier</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>Accident State</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>Policy Symbol</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>Policy Number</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>Policy MOD</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>Policy Effective Date_Source</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
         <is>
           <t>Policy Effective Date</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Expiration Date_Source</t>
-        </is>
-      </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="L1" s="25" t="inlineStr">
+        <is>
+          <t>Policy Expiration Date</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t>Producing Agent Code</t>
+        </is>
+      </c>
+      <c r="N1" s="25" t="inlineStr">
+        <is>
+          <t>Loss Date</t>
+        </is>
+      </c>
+      <c r="O1" s="25" t="inlineStr">
+        <is>
+          <t>Date of Notice (Report Date)</t>
+        </is>
+      </c>
+      <c r="P1" s="23" t="inlineStr">
+        <is>
+          <t>Lag Time</t>
+        </is>
+      </c>
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>Claim Status</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
+        <is>
+          <t>Claim Closed Date</t>
+        </is>
+      </c>
+      <c r="S1" s="23" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="T1" s="23" t="inlineStr">
+        <is>
+          <t>Cause Of Loss</t>
+        </is>
+      </c>
+      <c r="U1" s="23" t="inlineStr">
+        <is>
+          <t>Description Of Loss</t>
+        </is>
+      </c>
+      <c r="V1" s="23" t="inlineStr">
+        <is>
+          <t>Contributing Factor</t>
+        </is>
+      </c>
+      <c r="W1" s="28" t="inlineStr">
         <is>
           <t>Policy Holder Claim Number</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>Policy Expiration Date</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>Producing Agent Code</t>
-        </is>
-      </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="X1" s="28" t="inlineStr">
         <is>
           <t>Producing Agent Name</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>Claim Number</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>Feature Number</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="Q1" s="21" t="inlineStr">
-        <is>
-          <t>Loss Date_Source</t>
-        </is>
-      </c>
-      <c r="R1" s="12" t="inlineStr">
-        <is>
-          <t>Loss Date</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>Cause Of Loss</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>Description Of Loss</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>Contributing Factor</t>
-        </is>
-      </c>
-      <c r="V1" s="11" t="inlineStr">
+      <c r="Y1" s="28" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="W1" s="11" t="inlineStr">
+      <c r="Z1" s="28" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="X1" s="11" t="inlineStr">
+      <c r="AA1" s="28" t="inlineStr">
         <is>
           <t>Policy Region Description</t>
         </is>
       </c>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="AB1" s="28" t="inlineStr">
         <is>
           <t>Policy Holder Retailer Desc</t>
         </is>
       </c>
-      <c r="Z1" s="21" t="inlineStr">
-        <is>
-          <t>Reported Date_Source</t>
-        </is>
-      </c>
-      <c r="AA1" s="12" t="inlineStr">
-        <is>
-          <t>Reported Date</t>
-        </is>
-      </c>
-      <c r="AB1" s="9" t="inlineStr">
-        <is>
-          <t>Claim Status</t>
-        </is>
-      </c>
-      <c r="AC1" s="21" t="inlineStr">
-        <is>
-          <t>Claim Closed Date</t>
-        </is>
-      </c>
-      <c r="AD1" s="11" t="inlineStr">
+      <c r="AC1" s="28" t="inlineStr">
         <is>
           <t>Accident Day Of Week</t>
         </is>
       </c>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AD1" s="28" t="inlineStr">
         <is>
           <t>Adjuster</t>
         </is>
       </c>
-      <c r="AF1" s="11" t="inlineStr">
+      <c r="AE1" s="28" t="inlineStr">
         <is>
           <t>Adjuster Email</t>
         </is>
       </c>
-      <c r="AG1" s="11" t="inlineStr">
+      <c r="AF1" s="28" t="inlineStr">
         <is>
           <t>Adjuster Phone Number</t>
         </is>
       </c>
-      <c r="AH1" s="11" t="inlineStr">
+      <c r="AG1" s="28" t="inlineStr">
         <is>
           <t>Record Source Code</t>
         </is>
       </c>
-      <c r="AI1" s="11" t="inlineStr">
+      <c r="AH1" s="28" t="inlineStr">
         <is>
           <t>Record Only Indicator</t>
         </is>
       </c>
-      <c r="AJ1" s="11" t="inlineStr">
+      <c r="AI1" s="28" t="inlineStr">
         <is>
           <t>Exposure Indicator</t>
         </is>
       </c>
-      <c r="AK1" s="11" t="inlineStr">
+      <c r="AJ1" s="28" t="inlineStr">
         <is>
           <t>RO System Date</t>
         </is>
       </c>
-      <c r="AL1" s="12" t="inlineStr">
-        <is>
-          <t>Claim Closed Date</t>
-        </is>
-      </c>
-      <c r="AM1" s="9" t="inlineStr">
-        <is>
-          <t>Claimant Name - Company</t>
-        </is>
-      </c>
-      <c r="AN1" s="11" t="inlineStr">
+      <c r="AK1" s="28" t="inlineStr">
         <is>
           <t>Occupation</t>
         </is>
@@ -2188,20 +1814,23 @@
       <c r="B2" s="15" t="n"/>
       <c r="C2" s="15" t="n"/>
       <c r="D2" s="15" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="17" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
-      <c r="J2" s="15" t="n"/>
-      <c r="K2" s="22" t="n"/>
-      <c r="L2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="29" t="n"/>
+      <c r="L2" s="29" t="n"/>
       <c r="M2" s="15" t="n"/>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="15" t="n"/>
-      <c r="P2" s="15" t="n"/>
-      <c r="Q2" s="18" t="n"/>
-      <c r="R2" s="18" t="n"/>
+      <c r="N2" s="29" t="n"/>
+      <c r="O2" s="29" t="n"/>
+      <c r="P2" s="30">
+        <f>IF(OR(N2="",O2=""),"",INT(O2)-INT(N2))</f>
+        <v/>
+      </c>
+      <c r="Q2" s="15" t="n"/>
+      <c r="R2" s="29" t="n"/>
       <c r="S2" s="15" t="n"/>
       <c r="T2" s="15" t="n"/>
       <c r="U2" s="15" t="n"/>
@@ -2209,10 +1838,10 @@
       <c r="W2" s="15" t="n"/>
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="15" t="n"/>
-      <c r="Z2" s="18" t="n"/>
-      <c r="AA2" s="18" t="n"/>
+      <c r="Z2" s="15" t="n"/>
+      <c r="AA2" s="15" t="n"/>
       <c r="AB2" s="15" t="n"/>
-      <c r="AC2" s="18" t="n"/>
+      <c r="AC2" s="15" t="n"/>
       <c r="AD2" s="15" t="n"/>
       <c r="AE2" s="15" t="n"/>
       <c r="AF2" s="15" t="n"/>
@@ -2221,12 +1850,10 @@
       <c r="AI2" s="15" t="n"/>
       <c r="AJ2" s="15" t="n"/>
       <c r="AK2" s="15" t="n"/>
-      <c r="AL2" s="22" t="n"/>
-      <c r="AM2" s="15" t="n"/>
-      <c r="AN2" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN2"/>
+  <autoFilter ref="A1:AK2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>